--- a/src-tauri/samples/mame/09_mame_agilent_rep_batch.xlsx
+++ b/src-tauri/samples/mame/09_mame_agilent_rep_batch.xlsx
@@ -461,7 +461,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q232A_inj1</t>
+          <t>S65T_inj1</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -471,7 +471,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Q232A_inj2</t>
+          <t>S65T_inj2</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -481,7 +481,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q232A_inj3</t>
+          <t>S65T_inj3</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -491,7 +491,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y233A_inj1</t>
+          <t>Y66H_inj1</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -501,7 +501,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y233A_inj2</t>
+          <t>Y66H_inj2</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -511,7 +511,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y233A_inj3</t>
+          <t>Y66H_inj3</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -521,7 +521,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A40P_inj1</t>
+          <t>T203Y_inj1</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -531,7 +531,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A40P_inj2</t>
+          <t>T203Y_inj2</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -541,7 +541,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A40P_inj3</t>
+          <t>T203Y_inj3</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -551,7 +551,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E61Y_inj1</t>
+          <t>F64L_inj1</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -561,7 +561,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E61Y_inj2</t>
+          <t>F64L_inj2</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -571,7 +571,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E61Y_inj3</t>
+          <t>F64L_inj3</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -581,7 +581,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L150V_inj1</t>
+          <t>A206K_inj1</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -591,7 +591,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L150V_inj2</t>
+          <t>A206K_inj2</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -601,7 +601,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L150V_inj3</t>
+          <t>A206K_inj3</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -611,7 +611,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A40P_E61Y_inj1</t>
+          <t>S65A_inj1</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -621,7 +621,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A40P_E61Y_inj2</t>
+          <t>S65A_inj2</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -631,7 +631,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A40P_E61Y_inj3</t>
+          <t>S65A_inj3</t>
         </is>
       </c>
       <c r="B22" t="n">

--- a/src-tauri/samples/mame/09_mame_agilent_rep_batch.xlsx
+++ b/src-tauri/samples/mame/09_mame_agilent_rep_batch.xlsx
@@ -413,239 +413,931 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sample Name</t>
+          <t>Signal:</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>FID1B</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WT_inj1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>995.2</v>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>WT_inj2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>989.7</v>
+      <c r="A3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WT1</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WT_inj3</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1013.7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>S65T_inj1</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1845.1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S65T_inj2</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1837.8</v>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S65T_inj3</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1837.9</v>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Y66H_inj1</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>490.4</v>
+      <c r="A8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>WT2</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y66H_inj2</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>483.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Y66H_inj3</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>489.2</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T203Y_inj1</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2336.9</v>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T203Y_inj2</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2331.1</v>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>T203Y_inj3</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2344.2</v>
+      <c r="A13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>WT3</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F64L_inj1</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1546.4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>F64L_inj2</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1551.6</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F64L_inj3</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1559.9</v>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A206K_inj1</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1203.6</v>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A206K_inj2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1210.9</v>
+      <c r="A18" t="n">
+        <v>3180</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>65A</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A206K_inj3</t>
+          <t>Sum</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1202.3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>S65A_inj1</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>3116.1</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S65A_inj2</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3096.4</v>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S65A_inj3</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>3101.8</v>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>blank_inj1</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>12.3</v>
+      <c r="A23" t="n">
+        <v>3210</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>65A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3195</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>65A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2380</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>203Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2405</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>203Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2390</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>203Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1910</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>65T</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>65T</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>65T</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1580</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>64L</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1595</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>64L</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1570</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>64L</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>206K</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1235</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>206K</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>206K</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>510</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>66H</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>500</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>66H</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>520</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>66H</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>520</v>
       </c>
     </row>
   </sheetData>

--- a/src-tauri/samples/mame/09_mame_agilent_rep_batch.xlsx
+++ b/src-tauri/samples/mame/09_mame_agilent_rep_batch.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agilent" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Agilent" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,7 +442,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -457,8 +457,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1000</v>
-      </c>
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -486,7 +490,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1000</v>
+        <v>962</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -501,8 +505,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1000</v>
-      </c>
+        <v>962</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -530,7 +538,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1000</v>
+        <v>982</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -545,8 +553,12 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1000</v>
-      </c>
+        <v>982</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -574,11 +586,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3180</v>
+        <v>3132.3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>65A</t>
+          <t>168T</t>
         </is>
       </c>
     </row>
@@ -589,8 +601,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3180</v>
-      </c>
+        <v>3132.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -618,11 +634,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3210</v>
+        <v>3161.8</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>65A</t>
+          <t>168T</t>
         </is>
       </c>
     </row>
@@ -633,8 +649,12 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3210</v>
-      </c>
+        <v>3161.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -662,11 +682,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3195</v>
+        <v>2226.1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>65A</t>
+          <t>204Y</t>
         </is>
       </c>
     </row>
@@ -677,8 +697,12 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3195</v>
-      </c>
+        <v>2226.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -706,11 +730,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2380</v>
+        <v>2245.8</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>203Y</t>
+          <t>204Y</t>
         </is>
       </c>
     </row>
@@ -721,8 +745,12 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2380</v>
-      </c>
+        <v>2245.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -750,11 +778,11 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2405</v>
+        <v>1861.6</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>203Y</t>
+          <t>154T</t>
         </is>
       </c>
     </row>
@@ -765,8 +793,12 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2405</v>
-      </c>
+        <v>1861.6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -794,11 +826,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2390</v>
+        <v>1881.3</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>203Y</t>
+          <t>154T</t>
         </is>
       </c>
     </row>
@@ -809,536 +841,12 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2390</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>1910</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>65T</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>1895</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>65T</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>1905</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>65T</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1905</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>1580</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>64L</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>1580</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>1595</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>64L</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>1570</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>64L</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>1220</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>206K</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>1235</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>206K</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>1215</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>206K</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>510</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>66H</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>500</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>66H</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>520</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>66H</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>520</v>
-      </c>
+        <v>1881.3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src-tauri/samples/mame/09_mame_agilent_rep_batch.xlsx
+++ b/src-tauri/samples/mame/09_mame_agilent_rep_batch.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>168T</t>
+          <t>88V</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>168T</t>
+          <t>88V</t>
         </is>
       </c>
     </row>
@@ -682,11 +682,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2226.1</v>
+        <v>2324.6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>204Y</t>
+          <t>28A</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2226.1</v>
+        <v>2324.6</v>
       </c>
     </row>
     <row r="30">
@@ -730,11 +730,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2245.8</v>
+        <v>2354.2</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>204Y</t>
+          <t>28A</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2245.8</v>
+        <v>2354.2</v>
       </c>
     </row>
     <row r="35">
@@ -782,7 +782,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>154T</t>
+          <t>78A</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>154T</t>
+          <t>78A</t>
         </is>
       </c>
     </row>
